--- a/claude/v1/storage/excel/Codes_USSD_CI.xlsx
+++ b/claude/v1/storage/excel/Codes_USSD_CI.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11700"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="6990"/>
   </bookViews>
   <sheets>
     <sheet name="Codes USSD CI" sheetId="2" r:id="rId1"/>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>#124*34#</t>
-  </si>
-  <si>
-    <t>#99#</t>
   </si>
   <si>
     <t>#144#</t>
@@ -827,6 +824,9 @@
   </si>
   <si>
     <t>USSD_Code</t>
+  </si>
+  <si>
+    <t>*99#</t>
   </si>
 </sst>
 </file>
@@ -1264,37 +1264,37 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1305,25 +1305,25 @@
         <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="I2" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
@@ -1336,25 +1336,25 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="I3" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
@@ -1367,28 +1367,28 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="K4" s="3">
         <v>2</v>
@@ -1404,22 +1404,22 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="I5" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K5" s="6"/>
     </row>
@@ -1431,28 +1431,28 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="K6" s="6"/>
     </row>
@@ -1464,25 +1464,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="I7" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="3">
@@ -1497,25 +1497,25 @@
         <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>168</v>
-      </c>
       <c r="G8" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="3">
@@ -1532,19 +1532,19 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -1559,22 +1559,22 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K10" s="6"/>
     </row>
@@ -1586,25 +1586,25 @@
         <v>5</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="I11" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="3">
@@ -1619,28 +1619,28 @@
         <v>5</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="K12" s="3">
         <v>2</v>
@@ -1654,28 +1654,28 @@
         <v>5</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="K13" s="3">
         <v>2</v>
@@ -1691,19 +1691,19 @@
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="I14" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="3">
@@ -1720,22 +1720,22 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="I15" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K15" s="3">
         <v>2</v>
@@ -1749,25 +1749,25 @@
         <v>5</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="I16" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
@@ -1780,25 +1780,25 @@
         <v>5</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>8</v>
+        <v>208</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
@@ -1811,25 +1811,25 @@
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="I18" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
@@ -1842,25 +1842,25 @@
         <v>0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="I19" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
@@ -1873,25 +1873,25 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="I20" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
@@ -1904,25 +1904,25 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="I21" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
@@ -1935,28 +1935,28 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K22" s="6"/>
     </row>
@@ -1968,25 +1968,25 @@
         <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
@@ -1999,25 +1999,25 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
@@ -2030,25 +2030,25 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
@@ -2063,19 +2063,19 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
@@ -2090,19 +2090,19 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
@@ -2117,19 +2117,19 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
@@ -2144,19 +2144,19 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
@@ -2171,19 +2171,19 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="I30" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
@@ -2198,19 +2198,19 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="G31" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
@@ -2225,19 +2225,19 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="G32" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="I32" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
@@ -2250,25 +2250,25 @@
         <v>0</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E33" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="G33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="I33" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -2281,25 +2281,25 @@
         <v>0</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>8</v>
+        <v>208</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
@@ -2309,28 +2309,28 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="I35" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
@@ -2340,28 +2340,28 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E36" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="G36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="I36" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
@@ -2371,31 +2371,31 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K37" s="6"/>
     </row>
@@ -2404,24 +2404,24 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="I38" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
@@ -2431,31 +2431,31 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J39" s="9" t="s">
         <v>96</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>97</v>
       </c>
       <c r="K39" s="6"/>
     </row>
@@ -2464,31 +2464,31 @@
         <v>39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F40" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="G40" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="G40" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="I40" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K40" s="6"/>
     </row>
@@ -2497,31 +2497,31 @@
         <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F41" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G41" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>104</v>
-      </c>
       <c r="I41" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K41" s="6"/>
     </row>
@@ -2530,28 +2530,28 @@
         <v>41</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J42" s="9"/>
       <c r="K42" s="6"/>
@@ -2561,28 +2561,28 @@
         <v>42</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F43" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G43" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="I43" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
@@ -2592,31 +2592,31 @@
         <v>43</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K44" s="6"/>
     </row>
@@ -2625,31 +2625,31 @@
         <v>44</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K45" s="6"/>
     </row>
@@ -2658,31 +2658,31 @@
         <v>45</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E46" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F46" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F46" s="9" t="s">
-        <v>113</v>
-      </c>
       <c r="G46" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K46" s="6"/>
     </row>
@@ -2691,28 +2691,28 @@
         <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="G47" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="G47" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="I47" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="6"/>
@@ -2722,28 +2722,28 @@
         <v>47</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E48" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F48" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="G48" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G48" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>119</v>
-      </c>
       <c r="I48" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J48" s="9"/>
       <c r="K48" s="6"/>
@@ -2753,28 +2753,28 @@
         <v>48</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E49" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F49" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="G49" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G49" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>122</v>
-      </c>
       <c r="I49" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J49" s="9"/>
       <c r="K49" s="6"/>
@@ -2784,28 +2784,28 @@
         <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J50" s="9"/>
       <c r="K50" s="6"/>
@@ -2815,31 +2815,31 @@
         <v>50</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K51" s="6"/>
     </row>
@@ -2848,24 +2848,24 @@
         <v>51</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J52" s="9"/>
       <c r="K52" s="6"/>
@@ -2875,27 +2875,27 @@
         <v>52</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F53" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>127</v>
-      </c>
       <c r="G53" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H53" s="9" t="s">
         <v>3</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K53" s="6"/>
     </row>
@@ -2904,28 +2904,28 @@
         <v>53</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E54" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F54" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F54" s="9" t="s">
-        <v>129</v>
-      </c>
       <c r="G54" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J54" s="9"/>
       <c r="K54" s="6"/>
@@ -2935,31 +2935,31 @@
         <v>54</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H55" s="9" t="s">
-        <v>40</v>
-      </c>
       <c r="I55" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K55" s="3">
         <v>62</v>
@@ -2970,31 +2970,31 @@
         <v>55</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E56" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="F56" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F56" s="9" t="s">
-        <v>132</v>
-      </c>
       <c r="G56" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H56" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H56" s="9" t="s">
-        <v>40</v>
-      </c>
       <c r="I56" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K56" s="3">
         <v>62</v>
@@ -3005,31 +3005,31 @@
         <v>56</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F57" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>134</v>
-      </c>
       <c r="G57" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H57" s="9" t="s">
-        <v>40</v>
-      </c>
       <c r="I57" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K57" s="3">
         <v>62</v>
@@ -3040,31 +3040,31 @@
         <v>57</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F58" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J58" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="K58" s="3">
         <v>62</v>
@@ -3075,31 +3075,31 @@
         <v>58</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F59" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>137</v>
-      </c>
       <c r="G59" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H59" s="9" t="s">
-        <v>40</v>
-      </c>
       <c r="I59" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K59" s="3">
         <v>62</v>
@@ -3110,27 +3110,27 @@
         <v>59</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F60" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="G60" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="G60" s="10" t="s">
-        <v>140</v>
-      </c>
       <c r="H60" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K60" s="3">
         <v>62</v>
@@ -3141,31 +3141,31 @@
         <v>60</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E61" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F61" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="G61" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="G61" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>143</v>
-      </c>
       <c r="I61" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K61" s="3">
         <v>62</v>
@@ -3176,31 +3176,31 @@
         <v>61</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E62" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="F62" s="9" t="s">
-        <v>145</v>
-      </c>
       <c r="G62" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H62" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H62" s="9" t="s">
-        <v>40</v>
-      </c>
       <c r="I62" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K62" s="3">
         <v>62</v>
@@ -3211,31 +3211,31 @@
         <v>62</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>1</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K63" s="6"/>
     </row>
@@ -3244,31 +3244,31 @@
         <v>63</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K64" s="3">
         <v>62</v>
@@ -3279,31 +3279,31 @@
         <v>64</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E65" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F65" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>150</v>
-      </c>
       <c r="G65" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H65" s="9" t="s">
         <v>3</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K65" s="3">
         <v>62</v>
@@ -3314,31 +3314,31 @@
         <v>65</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K66" s="3">
         <v>62</v>
@@ -3349,31 +3349,31 @@
         <v>66</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F67" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="G67" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>155</v>
-      </c>
       <c r="I67" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K67" s="3">
         <v>62</v>
@@ -3384,27 +3384,27 @@
         <v>67</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F68" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H68" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="G68" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>158</v>
-      </c>
       <c r="I68" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K68" s="6"/>
     </row>
@@ -3413,27 +3413,27 @@
         <v>68</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K69" s="6"/>
     </row>
@@ -3442,28 +3442,28 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E70" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F70" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="G70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H70" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G70" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="I70" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
@@ -3473,28 +3473,28 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>8</v>
+        <v>208</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
@@ -3504,28 +3504,28 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E72" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="G72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G72" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="I72" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
@@ -3535,28 +3535,28 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>8</v>
+        <v>208</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
